--- a/tools/importer/reports/import-standard-page.report.xlsx
+++ b/tools/importer/reports/import-standard-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>service-page</t>
   </si>
   <si>
-    <t>2026-05-11T08:46:48.480Z</t>
+    <t>2026-05-11T17:55:01.980Z</t>
   </si>
   <si>
     <t>AI Services - NextRow</t>
@@ -70,7 +70,7 @@
     <t>b2b-marketing</t>
   </si>
   <si>
-    <t>2026-05-11T08:46:20.685Z</t>
+    <t>2026-05-11T17:54:34.921Z</t>
   </si>
   <si>
     <t>B2B Marketing - NextRow</t>
@@ -91,7 +91,7 @@
     <t>standard-page</t>
   </si>
   <si>
-    <t>2026-05-11T09:07:45.275Z</t>
+    <t>2026-05-11T17:56:42.291Z</t>
   </si>
   <si>
     <t>Insights - NextRow</t>
@@ -109,7 +109,7 @@
     <t>cloud-services</t>
   </si>
   <si>
-    <t>2026-05-11T08:46:54.153Z</t>
+    <t>2026-05-11T17:55:08.599Z</t>
   </si>
   <si>
     <t>Cloud Services - NextRow</t>
@@ -127,7 +127,7 @@
     <t>contact-us</t>
   </si>
   <si>
-    <t>2026-05-11T09:07:38.424Z</t>
+    <t>2026-05-11T17:56:35.278Z</t>
   </si>
   <si>
     <t>Contact Us - NextRow</t>
@@ -142,7 +142,7 @@
     <t>content-supply-chain</t>
   </si>
   <si>
-    <t>2026-05-11T08:46:34.909Z</t>
+    <t>2026-05-11T17:54:49.872Z</t>
   </si>
   <si>
     <t>Content Supply Chain - NextRow</t>
@@ -160,7 +160,7 @@
     <t>cyber-security</t>
   </si>
   <si>
-    <t>2026-05-11T08:47:06.639Z</t>
+    <t>2026-05-11T17:55:22.890Z</t>
   </si>
   <si>
     <t>Cyber Security - NextRow</t>
@@ -181,7 +181,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-11T08:31:19.694Z</t>
+    <t>2026-05-11T17:55:48.281Z</t>
   </si>
   <si>
     <t>NextRow Digital: Driving Business Growth Effectively - NextRow</t>
@@ -202,7 +202,7 @@
     <t>product-page</t>
   </si>
   <si>
-    <t>2026-05-11T08:57:38.728Z</t>
+    <t>2026-05-11T17:56:13.937Z</t>
   </si>
   <si>
     <t>Koru - NextRow</t>
@@ -217,7 +217,7 @@
     <t>martech-services</t>
   </si>
   <si>
-    <t>2026-05-11T08:46:41.728Z</t>
+    <t>2026-05-11T17:54:55.575Z</t>
   </si>
   <si>
     <t>MarTech Services | MarTech Business Solutions | NextRow Digital</t>
@@ -235,7 +235,7 @@
     <t>partners</t>
   </si>
   <si>
-    <t>2026-05-11T09:07:31.026Z</t>
+    <t>2026-05-11T17:56:28.546Z</t>
   </si>
   <si>
     <t>Partners - NextRow</t>
@@ -250,7 +250,7 @@
     <t>privacy-policy</t>
   </si>
   <si>
-    <t>2026-05-11T09:07:57.659Z</t>
+    <t>2026-05-11T17:56:54.935Z</t>
   </si>
   <si>
     <t>Privacy Policy - NextRow</t>
@@ -268,7 +268,7 @@
     <t>quiptag</t>
   </si>
   <si>
-    <t>2026-05-11T08:57:32.564Z</t>
+    <t>2026-05-11T17:56:07.321Z</t>
   </si>
   <si>
     <t>QuipTag: Accelerate Your Content Velocity - NextRow</t>
@@ -283,7 +283,7 @@
     <t>training</t>
   </si>
   <si>
-    <t>2026-05-11T09:07:51.660Z</t>
+    <t>2026-05-11T17:56:49.001Z</t>
   </si>
   <si>
     <t>AEM Training | Adobe Analytics Training | NextRow Digital</t>
@@ -298,7 +298,7 @@
     <t>unified-customer-experience</t>
   </si>
   <si>
-    <t>2026-05-11T08:46:28.641Z</t>
+    <t>2026-05-11T17:54:43.006Z</t>
   </si>
   <si>
     <t>Unified Customer Experience - NextRow</t>
@@ -313,7 +313,7 @@
     <t>workday-services</t>
   </si>
   <si>
-    <t>2026-05-11T08:47:00.299Z</t>
+    <t>2026-05-11T17:55:15.930Z</t>
   </si>
   <si>
     <t>Workday Services - NextRow</t>
@@ -328,7 +328,7 @@
     <t>snowflake-services/cloud-data-analytics</t>
   </si>
   <si>
-    <t>2026-05-11T08:47:12.381Z</t>
+    <t>2026-05-11T17:55:29.826Z</t>
   </si>
   <si>
     <t>Cloud Data Analytics - NextRow</t>
